--- a/data/trans_orig/Q5419_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>25429</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>18850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33571</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29334</t>
+          <t>29513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>11783</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>18766</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>25783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>345701</t>
+          <t>383117</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336963</t>
+          <t>374654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352340</t>
+          <t>389825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>564907</t>
+          <t>390552</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>538307</t>
+          <t>378738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>590088</t>
+          <t>399322</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>910609</t>
+          <t>773669</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887517</t>
+          <t>759216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>945539</t>
+          <t>785717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29099</t>
+          <t>31433</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73798</t>
+          <t>79365</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63610</t>
+          <t>68084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85670</t>
+          <t>93422</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>102896</t>
+          <t>110798</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>96366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118306</t>
+          <t>126224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>28666</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20453</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35319</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28582</t>
+          <t>29986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47374</t>
+          <t>48923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>26318</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51714</t>
+          <t>55895</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43008</t>
+          <t>46056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62047</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>69421</t>
+          <t>74616</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58471</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81585</t>
+          <t>88853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31071</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62815</t>
+          <t>69520</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53410</t>
+          <t>59590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72579</t>
+          <t>81169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>85394</t>
+          <t>92989</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71696</t>
+          <t>78950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97714</t>
+          <t>107473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202039</t>
+          <t>224769</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189146</t>
+          <t>211353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213366</t>
+          <t>237860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>208575</t>
+          <t>229002</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194061</t>
+          <t>213694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223890</t>
+          <t>245672</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>410614</t>
+          <t>453772</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>390676</t>
+          <t>432523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431095</t>
+          <t>473189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>281155</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>281155</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>281155</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>423931</t>
+          <t>462448</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>423931</t>
+          <t>462448</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>423931</t>
+          <t>462448</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>705086</t>
+          <t>770830</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>705086</t>
+          <t>770830</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>705086</t>
+          <t>770830</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>40117</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29539</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47104</t>
+          <t>51922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>88694</t>
+          <t>96110</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43050</t>
+          <t>83400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116320</t>
+          <t>109932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>136227</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>120194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150246</t>
+          <t>152367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30360</t>
+          <t>32748</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>42312</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>35467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>56993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23102</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>65888</t>
+          <t>71467</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>60792</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86249</t>
+          <t>85837</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>88990</t>
+          <t>96225</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58948</t>
+          <t>80529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>108177</t>
+          <t>112258</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37601</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>73464</t>
+          <t>81303</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>69719</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96229</t>
+          <t>95786</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>102658</t>
+          <t>111754</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67123</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124225</t>
+          <t>128613</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>547740</t>
+          <t>607887</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>531928</t>
+          <t>591632</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>560778</t>
+          <t>622981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>773482</t>
+          <t>619555</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>702232</t>
+          <t>596836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>913384</t>
+          <t>639596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1321222</t>
+          <t>1227442</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1263708</t>
+          <t>1201172</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1439393</t>
+          <t>1254667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
